--- a/artfynd/A 47250-2024 artfynd.xlsx
+++ b/artfynd/A 47250-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120852539</v>
+        <v>120852551</v>
       </c>
       <c r="B2" t="n">
-        <v>105284</v>
+        <v>82385</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>674</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Myskmåra</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Galium triflorum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>768937</v>
+        <v>768962</v>
       </c>
       <c r="R2" t="n">
-        <v>7343740</v>
+        <v>7343743</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120852569</v>
+        <v>120852550</v>
       </c>
       <c r="B3" t="n">
-        <v>105284</v>
+        <v>78601</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>674</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Myskmåra</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Galium triflorum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>768913</v>
+        <v>768936</v>
       </c>
       <c r="R3" t="n">
-        <v>7343730</v>
+        <v>7343736</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120852551</v>
+        <v>120852539</v>
       </c>
       <c r="B4" t="n">
-        <v>82382</v>
+        <v>105294</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>674</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Myskmåra</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Galium triflorum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>768962</v>
+        <v>768937</v>
       </c>
       <c r="R4" t="n">
-        <v>7343743</v>
+        <v>7343740</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120852540</v>
+        <v>120852569</v>
       </c>
       <c r="B5" t="n">
-        <v>78598</v>
+        <v>105294</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>674</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Myskmåra</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Galium triflorum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>769004</v>
+        <v>768913</v>
       </c>
       <c r="R5" t="n">
-        <v>7343748</v>
+        <v>7343730</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120852550</v>
+        <v>120852540</v>
       </c>
       <c r="B6" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>768936</v>
+        <v>769004</v>
       </c>
       <c r="R6" t="n">
-        <v>7343736</v>
+        <v>7343748</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 47250-2024 artfynd.xlsx
+++ b/artfynd/A 47250-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120852551</v>
+        <v>120852550</v>
       </c>
       <c r="B2" t="n">
-        <v>82385</v>
+        <v>78601</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>768962</v>
+        <v>768936</v>
       </c>
       <c r="R2" t="n">
-        <v>7343743</v>
+        <v>7343736</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120852550</v>
+        <v>120852551</v>
       </c>
       <c r="B3" t="n">
-        <v>78601</v>
+        <v>82385</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>768936</v>
+        <v>768962</v>
       </c>
       <c r="R3" t="n">
-        <v>7343736</v>
+        <v>7343743</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120852569</v>
+        <v>120852540</v>
       </c>
       <c r="B5" t="n">
-        <v>105294</v>
+        <v>78601</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>674</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Myskmåra</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Galium triflorum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>768913</v>
+        <v>769004</v>
       </c>
       <c r="R5" t="n">
-        <v>7343730</v>
+        <v>7343748</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120852540</v>
+        <v>120852569</v>
       </c>
       <c r="B6" t="n">
-        <v>78601</v>
+        <v>105294</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>674</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Myskmåra</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Galium triflorum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>769004</v>
+        <v>768913</v>
       </c>
       <c r="R6" t="n">
-        <v>7343748</v>
+        <v>7343730</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
